--- a/data/trans_orig/P79A9_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A9_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>864</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
